--- a/SK하이닉스_별도_결과.xlsx
+++ b/SK하이닉스_별도_결과.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>개별/별도재무제표(OFS) — 링크가 가리키는 문서('(첨부)재무제표') 기준으로 자동 선택됨</t>
+          <t>개별/별도재무제표(OFS)</t>
         </is>
       </c>
     </row>

--- a/SK하이닉스_별도_결과.xlsx
+++ b/SK하이닉스_별도_결과.xlsx
@@ -11,7 +11,8 @@
     <sheet name="재무제표" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="재무비율" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="상세보기_원항목추이" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="검증" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="스크리닝_전기당기증감" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="검증" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +43,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
     </font>
     <font>
       <b val="1"/>
@@ -73,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,15 +88,24 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FF4C4C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3075,7 +3089,1511 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:G59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="186" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>전기 대비 당기 증감 스크리닝 (분석적 절차)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>[안내] 재무상태표/손익계산서/현금흐름표의 개별 계정 중 전기 대비 증감률이 ±10%를 초과하는 계정만 추립니다(중요성 기준 미만 소액 계정은 제외). 신규계정(전기=0)·부호전환(흑자↔적자)은 %를 계산하지 않고 별도 표시합니다. 증감액(절대금액) 내림차순 정렬이며, ±30% 초과는 진하게, ±10~30%는 연하게 강조됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>[경고] 동일 계정명으로 매칭된 금액이 서로 달라 스크리닝에서 제외된 항목</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>[재무상태표] 기타금융부채: 동일 계정명으로 매칭된 금액이 서로 달라 스크리닝에서 제외됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>[재무상태표] 기타금융자산: 동일 계정명으로 매칭된 금액이 서로 달라 스크리닝에서 제외됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>[재무상태표] 기타수취채권: 동일 계정명으로 매칭된 금액이 서로 달라 스크리닝에서 제외됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>[재무상태표] 기타지급채무: 동일 계정명으로 매칭된 금액이 서로 달라 스크리닝에서 제외됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>[재무상태표] 리스부채: 동일 계정명으로 매칭된 금액이 서로 달라 스크리닝에서 제외됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>[재무상태표] 차입금: 동일 계정명으로 매칭된 금액이 서로 달라 스크리닝에서 제외됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>재무제표구분</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>계정명</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>전기금액</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>당기금액</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>증감액</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>증감률(%)</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>부채및자본총계</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>112412580000000</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>168903929000000</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>56491349000000</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>자산총계</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>112412580000000</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>168903929000000</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>56491349000000</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>자본총계</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>71227087000000</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>117318562000000</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>46091475000000</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>이익잉여금</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>65288998000000</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>106222565000000</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>40933567000000</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>비유동자산</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>85202229000000</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>122606991000000</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>37404762000000</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>포괄손익계산서</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>55736287000000</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>86852117000000</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>31115830000000</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>55.83</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>-17268506000000</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>-46588841000000</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>-29320335000000</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-169.79</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>포괄손익계산서</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>법인세비용차감전순이익(손실)</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>21271179000000</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>50058458000000</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>28787279000000</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>135.33</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>영업으로부터 창출된 현금흐름</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>24479468000000</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>51068852000000</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>26589384000000</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>108.62</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>포괄손익계산서</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>총포괄이익(손실)</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>17381347000000</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>42616584000000</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>25235237000000</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>145.19</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>포괄손익계산서</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>매출총이익(손실)</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>27580112000000</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>52760910000000</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>25180798000000</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>포괄손익계산서</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>당기순이익(손실)</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>17640396000000</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>42688817000000</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>25048421000000</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>141.99</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>24197084000000</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>48093510000000</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>23896426000000</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>98.76000000000001</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>포괄손익계산서</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>영업이익(손실)</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>21331452000000</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>44007409000000</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>22675957000000</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>유동자산</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>27210351000000</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>46296938000000</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>19086587000000</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>70.14</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>48316766000000</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>67394741000000</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>19077975000000</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>단기금융상품의 증가</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>1902500000000</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>15832500000000</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>13930000000000</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>732.1900000000001</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>포괄손익계산서</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>금융수익</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>4848298000000</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>17971786000000</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>13123488000000</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>270.68</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>유동부채</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>21577947000000</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>34536586000000</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>12958639000000</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>60.06</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>단기금융상품</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>1902500000000</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>14072500000000</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>12170000000000</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>639.6799999999999</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>유형자산의 취득</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>15140313000000</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>26085216000000</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>10944903000000</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>72.29000000000001</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>장기투자자산</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>3644169000000</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>14285809000000</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>10641640000000</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>292.02</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>부채총계</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>41185493000000</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>51585367000000</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>10399874000000</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>종속기업, 관계기업 및 공동기업투자</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>15112071000000</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>23555649000000</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>8443578000000</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>차입금의 상환</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>11877832000000</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>4235652000000</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>-7642180000000</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>-64.34</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>포괄손익계산서</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>금융비용</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>5085118000000</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>11984187000000</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>6899069000000</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>135.67</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>매출채권</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>10342858000000</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>16354297000000</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>6011439000000</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>58.12</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>포괄손익계산서</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>28156175000000</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>34091207000000</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>5935032000000</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>종속기업투자(MMT)의 순증감</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>-1728082000000</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>-7354446000000</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>-5626364000000</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>-325.58</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>법인세의 납부</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>281339000000</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>5628008000000</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>5346669000000</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>1900.44</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>-6874365000000</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>-2072321000000</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <v>4802044000000</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>자본잉여금</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>4465558000000</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>8778664000000</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>4313106000000</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>96.59</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>당기법인세부채</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>2966606000000</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>6890244000000</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>3923638000000</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>132.26</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>포괄손익계산서</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>법인세비용(수익)</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>3630783000000</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>7369641000000</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>3738858000000</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>102.98</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>단기금융상품의 감소</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>272500000000</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>3662500000000</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>3390000000000</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>1244.04</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>배당금의 수취</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>189614000000</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>2881608000000</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>2691994000000</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>1419.72</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>비유동부채</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>19607546000000</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>17048781000000</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>-2558765000000</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>-13.05</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>포괄손익계산서</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>판매비와관리비</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>6248660000000</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>8753501000000</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>2504841000000</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>차입금의 차입</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>6239628000000</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>4296456000000</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>-1943172000000</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>-31.14</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>기타수취채권의 감소</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>2218030000000</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>3620494000000</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>1402464000000</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>63.23</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>재고자산</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>9319917000000</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>10396303000000</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>1076386000000</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>미지급금</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>5280304000000</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>6298382000000</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>1018078000000</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>기타자본</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>-2191549000000</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>-1348598000000</v>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>842951000000</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>이연법인세자산</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>2016438000000</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>2789409000000</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>772971000000</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>2992694000000</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>2403922000000</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>-588772000000</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>-19.67</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>기말 현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>2992694000000</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>2403922000000</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>-588772000000</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>-19.67</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>매입채무</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>2824366000000</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>3317619000000</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>493253000000</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F13:F59">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="1">
+      <formula>30.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>-30.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="between" dxfId="0">
+      <formula>10.0</formula>
+      <formula>30.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="between" dxfId="0">
+      <formula>-30.0</formula>
+      <formula>-10.0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="125" customWidth="1" min="1" max="1"/>
@@ -3101,9 +4619,9 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>✓ 전체 15건 모두 일치 (검증 통과)</t>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>✓ 전체 158건 모두 일치 (검증 통과)</t>
         </is>
       </c>
     </row>
@@ -3523,6 +5041,3331 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>3) 전기 대비 당기 증감 스크리닝 검증 (원본금액 대사 + 증감률/분류 재계산 + 전수 검사)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>검증항목</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>기준값</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>재계산값</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>일치여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 부채및자본총계 (전기)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>112412580000000</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>112412580000000</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 부채및자본총계 (당기)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>168903929000000</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>168903929000000</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 부채및자본총계</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 자산총계 (전기)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>112412580000000</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>112412580000000</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 자산총계 (당기)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>168903929000000</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>168903929000000</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 자산총계</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 자본총계 (전기)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>71227087000000</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>71227087000000</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 자본총계 (당기)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>117318562000000</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>117318562000000</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 자본총계</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 이익잉여금 (전기)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>65288998000000</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>65288998000000</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 이익잉여금 (당기)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>106222565000000</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>106222565000000</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 이익잉여금</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 비유동자산 (전기)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>85202229000000</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>85202229000000</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 비유동자산 (당기)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>122606991000000</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>122606991000000</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 비유동자산</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 매출액 (전기)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>55736287000000</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>55736287000000</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 매출액 (당기)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>86852117000000</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>86852117000000</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 매출액</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>55.83</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>55.83</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 투자활동 현금흐름 (전기)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>-17268506000000</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>-17268506000000</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 투자활동 현금흐름 (당기)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>-46588841000000</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>-46588841000000</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>-169.79</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>-169.79</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 법인세비용차감전순이익(손실) (전기)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>21271179000000</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>21271179000000</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 법인세비용차감전순이익(손실) (당기)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>50058458000000</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>50058458000000</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 법인세비용차감전순이익(손실)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>135.33</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>135.33</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 영업으로부터 창출된 현금흐름 (전기)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>24479468000000</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>24479468000000</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 영업으로부터 창출된 현금흐름 (당기)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>51068852000000</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>51068852000000</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 영업으로부터 창출된 현금흐름</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>108.62</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>108.62</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 총포괄이익(손실) (전기)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>17381347000000</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>17381347000000</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 총포괄이익(손실) (당기)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>42616584000000</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>42616584000000</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 총포괄이익(손실)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>145.19</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>145.19</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 매출총이익(손실) (전기)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>27580112000000</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>27580112000000</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 매출총이익(손실) (당기)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>52760910000000</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>52760910000000</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 매출총이익(손실)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 당기순이익(손실) (전기)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>17640396000000</v>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>17640396000000</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 당기순이익(손실) (당기)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>42688817000000</v>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>42688817000000</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 당기순이익(손실)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>141.99</v>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>141.99</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 영업활동 현금흐름 (전기)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>24197084000000</v>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>24197084000000</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 영업활동 현금흐름 (당기)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>48093510000000</v>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>48093510000000</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>98.76000000000001</v>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>98.76000000000001</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 영업이익(손실) (전기)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>21331452000000</v>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>21331452000000</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 영업이익(손실) (당기)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>44007409000000</v>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>44007409000000</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 영업이익(손실)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 유동자산 (전기)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>27210351000000</v>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>27210351000000</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 유동자산 (당기)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>46296938000000</v>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>46296938000000</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 유동자산</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>70.14</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>70.14</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 유형자산 (전기)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>48316766000000</v>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>48316766000000</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 유형자산 (당기)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>67394741000000</v>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>67394741000000</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 유형자산</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 단기금융상품의 증가 (전기)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>1902500000000</v>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>1902500000000</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 단기금융상품의 증가 (당기)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>15832500000000</v>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>15832500000000</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 단기금융상품의 증가</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>732.1900000000001</v>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>732.1900000000001</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 금융수익 (전기)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>4848298000000</v>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>4848298000000</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 금융수익 (당기)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>17971786000000</v>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>17971786000000</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 금융수익</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>270.68</v>
+      </c>
+      <c r="D84" s="5" t="n">
+        <v>270.68</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 유동부채 (전기)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>21577947000000</v>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>21577947000000</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 유동부채 (당기)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>34536586000000</v>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>34536586000000</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 유동부채</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>60.06</v>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>60.06</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 단기금융상품 (전기)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="n">
+        <v>1902500000000</v>
+      </c>
+      <c r="D88" s="5" t="n">
+        <v>1902500000000</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 단기금융상품 (당기)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>14072500000000</v>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>14072500000000</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 단기금융상품</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="n">
+        <v>639.6799999999999</v>
+      </c>
+      <c r="D90" s="5" t="n">
+        <v>639.6799999999999</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 유형자산의 취득 (전기)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>15140313000000</v>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>15140313000000</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 유형자산의 취득 (당기)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="n">
+        <v>26085216000000</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>26085216000000</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 유형자산의 취득</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>72.29000000000001</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>72.29000000000001</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 장기투자자산 (전기)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="n">
+        <v>3644169000000</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>3644169000000</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 장기투자자산 (당기)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>14285809000000</v>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>14285809000000</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 장기투자자산</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>292.02</v>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>292.02</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 부채총계 (전기)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>41185493000000</v>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>41185493000000</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 부채총계 (당기)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="n">
+        <v>51585367000000</v>
+      </c>
+      <c r="D98" s="5" t="n">
+        <v>51585367000000</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 부채총계</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 종속기업, 관계기업 및 공동기업투자 (전기)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="n">
+        <v>15112071000000</v>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>15112071000000</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 종속기업, 관계기업 및 공동기업투자 (당기)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>23555649000000</v>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>23555649000000</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 종속기업, 관계기업 및 공동기업투자</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 차입금의 상환 (전기)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>11877832000000</v>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>11877832000000</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 차입금의 상환 (당기)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>4235652000000</v>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>4235652000000</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 차입금의 상환</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>-64.34</v>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>-64.34</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 금융비용 (전기)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>5085118000000</v>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>5085118000000</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 금융비용 (당기)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>11984187000000</v>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>11984187000000</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 금융비용</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="n">
+        <v>135.67</v>
+      </c>
+      <c r="D108" s="5" t="n">
+        <v>135.67</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 매출채권 (전기)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="n">
+        <v>10342858000000</v>
+      </c>
+      <c r="D109" s="5" t="n">
+        <v>10342858000000</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 매출채권 (당기)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="n">
+        <v>16354297000000</v>
+      </c>
+      <c r="D110" s="5" t="n">
+        <v>16354297000000</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 매출채권</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>58.12</v>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>58.12</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 매출원가 (전기)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="n">
+        <v>28156175000000</v>
+      </c>
+      <c r="D112" s="5" t="n">
+        <v>28156175000000</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 매출원가 (당기)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>34091207000000</v>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>34091207000000</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 매출원가</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 종속기업투자(MMT)의 순증감 (전기)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>-1728082000000</v>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>-1728082000000</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 종속기업투자(MMT)의 순증감 (당기)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="n">
+        <v>-7354446000000</v>
+      </c>
+      <c r="D116" s="5" t="n">
+        <v>-7354446000000</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 종속기업투자(MMT)의 순증감</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="n">
+        <v>-325.58</v>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>-325.58</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 법인세의 납부 (전기)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>281339000000</v>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>281339000000</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 법인세의 납부 (당기)</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>5628008000000</v>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>5628008000000</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 법인세의 납부</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="n">
+        <v>1900.44</v>
+      </c>
+      <c r="D120" s="5" t="n">
+        <v>1900.44</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 재무활동 현금흐름 (전기)</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>-6874365000000</v>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>-6874365000000</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 재무활동 현금흐름 (당기)</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="n">
+        <v>-2072321000000</v>
+      </c>
+      <c r="D122" s="5" t="n">
+        <v>-2072321000000</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 자본잉여금 (전기)</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="n">
+        <v>4465558000000</v>
+      </c>
+      <c r="D124" s="5" t="n">
+        <v>4465558000000</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 자본잉여금 (당기)</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="n">
+        <v>8778664000000</v>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>8778664000000</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 자본잉여금</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="n">
+        <v>96.59</v>
+      </c>
+      <c r="D126" s="5" t="n">
+        <v>96.59</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 당기법인세부채 (전기)</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="n">
+        <v>2966606000000</v>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>2966606000000</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 당기법인세부채 (당기)</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="n">
+        <v>6890244000000</v>
+      </c>
+      <c r="D128" s="5" t="n">
+        <v>6890244000000</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 당기법인세부채</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="n">
+        <v>132.26</v>
+      </c>
+      <c r="D129" s="5" t="n">
+        <v>132.26</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 법인세비용(수익) (전기)</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="n">
+        <v>3630783000000</v>
+      </c>
+      <c r="D130" s="5" t="n">
+        <v>3630783000000</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 법인세비용(수익) (당기)</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="n">
+        <v>7369641000000</v>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>7369641000000</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 법인세비용(수익)</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="n">
+        <v>102.98</v>
+      </c>
+      <c r="D132" s="5" t="n">
+        <v>102.98</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 단기금융상품의 감소 (전기)</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="n">
+        <v>272500000000</v>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>272500000000</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 단기금융상품의 감소 (당기)</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="n">
+        <v>3662500000000</v>
+      </c>
+      <c r="D134" s="5" t="n">
+        <v>3662500000000</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 단기금융상품의 감소</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="n">
+        <v>1244.04</v>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>1244.04</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 배당금의 수취 (전기)</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="n">
+        <v>189614000000</v>
+      </c>
+      <c r="D136" s="5" t="n">
+        <v>189614000000</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 배당금의 수취 (당기)</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="n">
+        <v>2881608000000</v>
+      </c>
+      <c r="D137" s="5" t="n">
+        <v>2881608000000</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 배당금의 수취</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="n">
+        <v>1419.72</v>
+      </c>
+      <c r="D138" s="5" t="n">
+        <v>1419.72</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 비유동부채 (전기)</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="n">
+        <v>19607546000000</v>
+      </c>
+      <c r="D139" s="5" t="n">
+        <v>19607546000000</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 비유동부채 (당기)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="n">
+        <v>17048781000000</v>
+      </c>
+      <c r="D140" s="5" t="n">
+        <v>17048781000000</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 비유동부채</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="n">
+        <v>-13.05</v>
+      </c>
+      <c r="D141" s="5" t="n">
+        <v>-13.05</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 판매비와관리비 (전기)</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="n">
+        <v>6248660000000</v>
+      </c>
+      <c r="D142" s="5" t="n">
+        <v>6248660000000</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 판매비와관리비 (당기)</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="n">
+        <v>8753501000000</v>
+      </c>
+      <c r="D143" s="5" t="n">
+        <v>8753501000000</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 판매비와관리비</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="D144" s="5" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 차입금의 차입 (전기)</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="n">
+        <v>6239628000000</v>
+      </c>
+      <c r="D145" s="5" t="n">
+        <v>6239628000000</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 차입금의 차입 (당기)</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="n">
+        <v>4296456000000</v>
+      </c>
+      <c r="D146" s="5" t="n">
+        <v>4296456000000</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 차입금의 차입</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="n">
+        <v>-31.14</v>
+      </c>
+      <c r="D147" s="5" t="n">
+        <v>-31.14</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기타수취채권의 감소 (전기)</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="n">
+        <v>2218030000000</v>
+      </c>
+      <c r="D148" s="5" t="n">
+        <v>2218030000000</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기타수취채권의 감소 (당기)</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="n">
+        <v>3620494000000</v>
+      </c>
+      <c r="D149" s="5" t="n">
+        <v>3620494000000</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 기타수취채권의 감소</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="n">
+        <v>63.23</v>
+      </c>
+      <c r="D150" s="5" t="n">
+        <v>63.23</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 재고자산 (전기)</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="n">
+        <v>9319917000000</v>
+      </c>
+      <c r="D151" s="5" t="n">
+        <v>9319917000000</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 재고자산 (당기)</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="n">
+        <v>10396303000000</v>
+      </c>
+      <c r="D152" s="5" t="n">
+        <v>10396303000000</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 재고자산</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="D153" s="5" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 미지급금 (전기)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="n">
+        <v>5280304000000</v>
+      </c>
+      <c r="D154" s="5" t="n">
+        <v>5280304000000</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 미지급금 (당기)</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="n">
+        <v>6298382000000</v>
+      </c>
+      <c r="D155" s="5" t="n">
+        <v>6298382000000</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 미지급금</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="D156" s="5" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 기타자본 (전기)</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="n">
+        <v>-2191549000000</v>
+      </c>
+      <c r="D157" s="5" t="n">
+        <v>-2191549000000</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 기타자본 (당기)</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="n">
+        <v>-1348598000000</v>
+      </c>
+      <c r="D158" s="5" t="n">
+        <v>-1348598000000</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 기타자본</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="D159" s="5" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 이연법인세자산 (전기)</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="n">
+        <v>2016438000000</v>
+      </c>
+      <c r="D160" s="5" t="n">
+        <v>2016438000000</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 이연법인세자산 (당기)</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="n">
+        <v>2789409000000</v>
+      </c>
+      <c r="D161" s="5" t="n">
+        <v>2789409000000</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 이연법인세자산</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="D162" s="5" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 현금및현금성자산 (전기)</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="n">
+        <v>2992694000000</v>
+      </c>
+      <c r="D163" s="5" t="n">
+        <v>2992694000000</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 현금및현금성자산 (당기)</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="n">
+        <v>2403922000000</v>
+      </c>
+      <c r="D164" s="5" t="n">
+        <v>2403922000000</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="n">
+        <v>-19.67</v>
+      </c>
+      <c r="D165" s="5" t="n">
+        <v>-19.67</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기말 현금및현금성자산 (전기)</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="n">
+        <v>2992694000000</v>
+      </c>
+      <c r="D166" s="5" t="n">
+        <v>2992694000000</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기말 현금및현금성자산 (당기)</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="n">
+        <v>2403922000000</v>
+      </c>
+      <c r="D167" s="5" t="n">
+        <v>2403922000000</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 기말 현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="n">
+        <v>-19.67</v>
+      </c>
+      <c r="D168" s="5" t="n">
+        <v>-19.67</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 매입채무 (전기)</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="n">
+        <v>2824366000000</v>
+      </c>
+      <c r="D169" s="5" t="n">
+        <v>2824366000000</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 매입채무 (당기)</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="n">
+        <v>3317619000000</v>
+      </c>
+      <c r="D170" s="5" t="n">
+        <v>3317619000000</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 매입채무</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="D171" s="5" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>스크리닝 완전성(포함됐어야 할 계정 누락 없음)</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>스크리닝 정확성(기준 미달 오탐 없음)</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SK하이닉스_별도_결과.xlsx
+++ b/SK하이닉스_별도_결과.xlsx
@@ -94,18 +94,12 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FF4C4C"/>
+          <fgColor rgb="00FFFF00"/>
+          <bgColor rgb="00FFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1080,9 +1074,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1092,7 +1086,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -2745,7 +2738,7 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -2759,7 +2752,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -2940,14 +2932,6 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E4:E11">
-    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
-      <formula>20</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="lessThanOrEqual" dxfId="0">
-      <formula>-20</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -2962,10 +2946,10 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="91" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2982,7 +2966,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2990,7 +2973,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -3089,33 +3071,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="186" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>전기 대비 당기 증감 스크리닝 (분석적 절차)</t>
+          <t>전기 대비 당기 증감 스크리닝</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>[안내] 재무상태표/손익계산서/현금흐름표의 개별 계정 중 전기 대비 증감률이 ±10%를 초과하는 계정만 추립니다(중요성 기준 미만 소액 계정은 제외). 신규계정(전기=0)·부호전환(흑자↔적자)은 %를 계산하지 않고 별도 표시합니다. 증감액(절대금액) 내림차순 정렬이며, ±30% 초과는 진하게, ±10~30%는 연하게 강조됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>[안내] 재무상태표/손익계산서/현금흐름표의 개별 계정 중 전기 대비 증감률이 ±10%를 초과하는 계정만 추립니다(중요성 기준 미만 소액 계정은 제외, 포함 여부는 전기→당기 기준). 신규계정(전기=0)·부호전환(흑자↔적자)은 %를 계산하지 않고 별도 표시합니다. 재무제표구분(재무상태표→손익계산서→현금흐름표) 순으로 묶은 뒤 그 안에서 증감액(절대금액) 내림차순 정렬하며, ±30% 초과인 계정은 '전기→당기 증감률(%)' 칸이 노란색으로 강조됩니다. '구분'이 "증감률초과"인 항목은 통상적으로 계산된 증감률이 기준을 넘었다는 뜻이며(문제가 없다는 뜻이 아님), 신규계정/부호전환은 애초에 %를 계산할 수 없어 별도 분류된 것입니다. '전전기→전기 증감률(%)'은 비교 참고용이며, 두 구간의 증감률 차이가 40%p 이상이면(둘 다 정상 계산된 경우에 한함) '추세이탈'에 표시됩니다 — 단순히 증감률이 큰 게 아니라 이번 기에 갑자기 패턴이 바뀐 계정을 잡아내기 위함입니다.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -3165,7 +3149,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
@@ -3179,25 +3162,40 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
+          <t>전전기금액</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
           <t>전기금액</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>당기금액</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>증감액</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>증감률(%)</t>
-        </is>
-      </c>
       <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>전기→당기 증감률(%)</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>전전기→전기 증감률(%)</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
@@ -3215,20 +3213,26 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
+        <v>92949387000000</v>
+      </c>
+      <c r="D13" s="7" t="n">
         <v>112412580000000</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="E13" s="7" t="n">
         <v>168903929000000</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="F13" s="7" t="n">
         <v>56491349000000</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="G13" s="5" t="n">
         <v>50.25</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>정상</t>
+      <c r="H13" s="5" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -3244,20 +3248,26 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
+        <v>92949387000000</v>
+      </c>
+      <c r="D14" s="7" t="n">
         <v>112412580000000</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="E14" s="7" t="n">
         <v>168903929000000</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="F14" s="7" t="n">
         <v>56491349000000</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="G14" s="5" t="n">
         <v>50.25</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>정상</t>
+      <c r="H14" s="5" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -3273,20 +3283,26 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
+        <v>54518322000000</v>
+      </c>
+      <c r="D15" s="7" t="n">
         <v>71227087000000</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="E15" s="7" t="n">
         <v>117318562000000</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="F15" s="7" t="n">
         <v>46091475000000</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="G15" s="5" t="n">
         <v>64.70999999999999</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>정상</t>
+      <c r="H15" s="5" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -3302,20 +3318,26 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
+        <v>48734611000000</v>
+      </c>
+      <c r="D16" s="7" t="n">
         <v>65288998000000</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="E16" s="7" t="n">
         <v>106222565000000</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="F16" s="7" t="n">
         <v>40933567000000</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="G16" s="5" t="n">
         <v>62.7</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>정상</t>
+      <c r="H16" s="5" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -3331,281 +3353,361 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
+        <v>75198085000000</v>
+      </c>
+      <c r="D17" s="7" t="n">
         <v>85202229000000</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="E17" s="7" t="n">
         <v>122606991000000</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="F17" s="7" t="n">
         <v>37404762000000</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="G17" s="5" t="n">
         <v>43.9</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>정상</t>
+      <c r="H17" s="5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>포괄손익계산서</t>
+          <t>재무상태표</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>매출액</t>
+          <t>유동자산</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>55736287000000</v>
+        <v>17751302000000</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>86852117000000</v>
+        <v>27210351000000</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>31115830000000</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>55.83</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>46296938000000</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>19086587000000</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>70.14</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>53.29</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>현금흐름표</t>
+          <t>재무상태표</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>투자활동 현금흐름</t>
+          <t>유형자산</t>
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>-17268506000000</v>
+        <v>38974277000000</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>-46588841000000</v>
+        <v>48316766000000</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>-29320335000000</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>-169.79</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>67394741000000</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>19077975000000</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>23.97</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>포괄손익계산서</t>
+          <t>재무상태표</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>법인세비용차감전순이익(손실)</t>
+          <t>유동부채</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>21271179000000</v>
+        <v>16197793000000</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>50058458000000</v>
+        <v>21577947000000</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>28787279000000</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>135.33</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>34536586000000</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>12958639000000</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>60.06</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>33.22</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>현금흐름표</t>
+          <t>재무상태표</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>영업으로부터 창출된 현금흐름</t>
+          <t>단기금융상품</t>
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>24479468000000</v>
+        <v>272500000000</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>51068852000000</v>
+        <v>1902500000000</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>26589384000000</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>108.62</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>14072500000000</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>12170000000000</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>639.6799999999999</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>598.17</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>포괄손익계산서</t>
+          <t>재무상태표</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>총포괄이익(손실)</t>
+          <t>장기투자자산</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>17381347000000</v>
+        <v>3765853000000</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>42616584000000</v>
+        <v>3644169000000</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>25235237000000</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>145.19</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>14285809000000</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>10641640000000</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>292.02</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>포괄손익계산서</t>
+          <t>재무상태표</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>매출총이익(손실)</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>27580112000000</v>
+        <v>38431065000000</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>52760910000000</v>
+        <v>41185493000000</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>25180798000000</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>91.3</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>51585367000000</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>10399874000000</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>포괄손익계산서</t>
+          <t>재무상태표</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>당기순이익(손실)</t>
+          <t>종속기업, 관계기업 및 공동기업투자</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>17640396000000</v>
+        <v>12694398000000</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>42688817000000</v>
+        <v>15112071000000</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>25048421000000</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>141.99</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>23555649000000</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>8443578000000</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>현금흐름표</t>
+          <t>재무상태표</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>영업활동 현금흐름</t>
+          <t>매출채권</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>24197084000000</v>
+        <v>3899437000000</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>48093510000000</v>
+        <v>10342858000000</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>23896426000000</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>98.76000000000001</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>16354297000000</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>6011439000000</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>58.12</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>165.24</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>포괄손익계산서</t>
+          <t>재무상태표</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>영업이익(손실)</t>
+          <t>자본잉여금</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>21331452000000</v>
+        <v>4389563000000</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>44007409000000</v>
+        <v>4465558000000</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>22675957000000</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>106.3</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>8778664000000</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>4313106000000</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>96.59</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -3617,24 +3719,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>유동자산</t>
+          <t>당기법인세부채</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>27210351000000</v>
+        <v>4484000000</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>46296938000000</v>
+        <v>2966606000000</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>19086587000000</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>70.14</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>6890244000000</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>3923638000000</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>132.26</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>66059.81</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -3646,82 +3759,105 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>유형자산</t>
+          <t>비유동부채</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>48316766000000</v>
+        <v>22233272000000</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>67394741000000</v>
+        <v>19607546000000</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>19077975000000</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>39.49</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>17048781000000</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>-2558765000000</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-13.05</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-11.81</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>현금흐름표</t>
+          <t>재무상태표</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>단기금융상품의 증가</t>
+          <t>재고자산</t>
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>1902500000000</v>
+        <v>8769507000000</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>15832500000000</v>
+        <v>9319917000000</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>13930000000000</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>732.1900000000001</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>10396303000000</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>1076386000000</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>포괄손익계산서</t>
+          <t>재무상태표</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>금융수익</t>
+          <t>미지급금</t>
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>4848298000000</v>
+        <v>3057580000000</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>17971786000000</v>
+        <v>5280304000000</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>13123488000000</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>270.68</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>6298382000000</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>1018078000000</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -3733,24 +3869,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>유동부채</t>
+          <t>기타자본</t>
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>21577947000000</v>
+        <v>-2269294000000</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>34536586000000</v>
+        <v>-2191549000000</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>12958639000000</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>60.06</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>-1348598000000</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>842951000000</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -3762,53 +3904,70 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>단기금융상품</t>
+          <t>이연법인세자산</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>1902500000000</v>
+        <v>2318089000000</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>14072500000000</v>
+        <v>2016438000000</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>12170000000000</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>639.6799999999999</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>2789409000000</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>772971000000</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>-13.01</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>현금흐름표</t>
+          <t>재무상태표</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>유형자산의 취득</t>
+          <t>현금및현금성자산</t>
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>15140313000000</v>
+        <v>2898074000000</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>26085216000000</v>
+        <v>2992694000000</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>10944903000000</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>72.29000000000001</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>2403922000000</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>-588772000000</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>-19.67</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -3820,111 +3979,134 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>장기투자자산</t>
+          <t>매입채무</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>3644169000000</v>
+        <v>2410182000000</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>14285809000000</v>
+        <v>2824366000000</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>10641640000000</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>292.02</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>3317619000000</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>493253000000</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>재무상태표</t>
+          <t>포괄손익계산서</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>매출액</t>
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>41185493000000</v>
+        <v>27639997000000</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>51585367000000</v>
+        <v>55736287000000</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>10399874000000</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>25.25</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>86852117000000</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>31115830000000</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>55.83</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>재무상태표</t>
+          <t>포괄손익계산서</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>종속기업, 관계기업 및 공동기업투자</t>
+          <t>법인세비용차감전순이익(손실)</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>15112071000000</v>
+        <v>-7578702000000</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>23555649000000</v>
+        <v>21271179000000</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>8443578000000</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>55.87</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>50058458000000</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>28787279000000</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>135.33</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>현금흐름표</t>
+          <t>포괄손익계산서</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>차입금의 상환</t>
+          <t>총포괄이익(손실)</t>
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>11877832000000</v>
+        <v>-4874603000000</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>4235652000000</v>
+        <v>17381347000000</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-7642180000000</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>-64.34</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>42616584000000</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>25235237000000</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>145.19</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -3936,53 +4118,67 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>금융비용</t>
+          <t>매출총이익(손실)</t>
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>5085118000000</v>
+        <v>447119000000</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>11984187000000</v>
+        <v>27580112000000</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>6899069000000</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>135.67</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>52760910000000</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>25180798000000</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>6068.41</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>재무상태표</t>
+          <t>포괄손익계산서</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>매출채권</t>
+          <t>당기순이익(손실)</t>
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>10342858000000</v>
+        <v>-4836170000000</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>16354297000000</v>
+        <v>17640396000000</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>6011439000000</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>58.12</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>42688817000000</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>25048421000000</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>141.99</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -3994,198 +4190,249 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>매출원가</t>
+          <t>영업이익(손실)</t>
         </is>
       </c>
       <c r="C40" s="7" t="n">
-        <v>28156175000000</v>
+        <v>-4672124000000</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>34091207000000</v>
+        <v>21331452000000</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>5935032000000</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>21.08</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>44007409000000</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>22675957000000</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>현금흐름표</t>
+          <t>포괄손익계산서</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>종속기업투자(MMT)의 순증감</t>
+          <t>금융수익</t>
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>-1728082000000</v>
+        <v>2189851000000</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>-7354446000000</v>
+        <v>4848298000000</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-5626364000000</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>-325.58</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>17971786000000</v>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>13123488000000</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>270.68</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>121.4</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>현금흐름표</t>
+          <t>포괄손익계산서</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>법인세의 납부</t>
+          <t>금융비용</t>
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>281339000000</v>
+        <v>5133547000000</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>5628008000000</v>
+        <v>5085118000000</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>5346669000000</v>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>1900.44</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>11984187000000</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>6899069000000</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>135.67</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>현금흐름표</t>
+          <t>포괄손익계산서</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>재무활동 현금흐름</t>
+          <t>매출원가</t>
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>-6874365000000</v>
+        <v>27192878000000</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>-2072321000000</v>
+        <v>28156175000000</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>4802044000000</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>69.84999999999999</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>34091207000000</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>5935032000000</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>재무상태표</t>
+          <t>포괄손익계산서</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>자본잉여금</t>
+          <t>법인세비용(수익)</t>
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>4465558000000</v>
+        <v>-2742532000000</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>8778664000000</v>
+        <v>3630783000000</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>4313106000000</v>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>96.59</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>7369641000000</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>3738858000000</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>102.98</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>재무상태표</t>
+          <t>포괄손익계산서</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>당기법인세부채</t>
+          <t>판매비와관리비</t>
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>2966606000000</v>
+        <v>5119243000000</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>6890244000000</v>
+        <v>6248660000000</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>3923638000000</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>132.26</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>8753501000000</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>2504841000000</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>22.06</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>포괄손익계산서</t>
+          <t>현금흐름표</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>법인세비용(수익)</t>
+          <t>투자활동 현금흐름</t>
         </is>
       </c>
       <c r="C46" s="7" t="n">
-        <v>3630783000000</v>
+        <v>-9232773000000</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>7369641000000</v>
+        <v>-17268506000000</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>3738858000000</v>
-      </c>
-      <c r="F46" s="5" t="n">
-        <v>102.98</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>-46588841000000</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>-29320335000000</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>-169.79</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>-87.03</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -4197,24 +4444,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>단기금융상품의 감소</t>
+          <t>영업으로부터 창출된 현금흐름</t>
         </is>
       </c>
       <c r="C47" s="7" t="n">
-        <v>272500000000</v>
+        <v>4888159000000</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>3662500000000</v>
+        <v>24479468000000</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>3390000000000</v>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>1244.04</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>51068852000000</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>26589384000000</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>108.62</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>400.79</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -4226,82 +4484,107 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>배당금의 수취</t>
+          <t>영업활동 현금흐름</t>
         </is>
       </c>
       <c r="C48" s="7" t="n">
-        <v>189614000000</v>
+        <v>3591547000000</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>2881608000000</v>
+        <v>24197084000000</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>2691994000000</v>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>1419.72</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>48093510000000</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>23896426000000</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>98.76000000000001</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>573.72</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>재무상태표</t>
+          <t>현금흐름표</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>비유동부채</t>
+          <t>단기금융상품의 증가</t>
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>19607546000000</v>
+        <v>0</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>17048781000000</v>
+        <v>1902500000000</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>-2558765000000</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>-13.05</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>15832500000000</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>13930000000000</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>732.1900000000001</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>포괄손익계산서</t>
+          <t>현금흐름표</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>판매비와관리비</t>
+          <t>유형자산의 취득</t>
         </is>
       </c>
       <c r="C50" s="7" t="n">
-        <v>6248660000000</v>
+        <v>6707400000000</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>8753501000000</v>
+        <v>15140313000000</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>2504841000000</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>40.09</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>26085216000000</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>10944903000000</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>72.29000000000001</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>125.73</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -4313,24 +4596,35 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>차입금의 차입</t>
+          <t>차입금의 상환</t>
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>6239628000000</v>
+        <v>9015663000000</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>4296456000000</v>
+        <v>11877832000000</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-1943172000000</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>-31.14</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>4235652000000</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>-7642180000000</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>-64.34</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -4342,169 +4636,214 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>기타수취채권의 감소</t>
+          <t>종속기업투자(MMT)의 순증감</t>
         </is>
       </c>
       <c r="C52" s="7" t="n">
-        <v>2218030000000</v>
+        <v>-755395000000</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>3620494000000</v>
+        <v>-1728082000000</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>1402464000000</v>
-      </c>
-      <c r="F52" s="5" t="n">
-        <v>63.23</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>-7354446000000</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>-5626364000000</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>-325.58</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>-128.77</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>재무상태표</t>
+          <t>현금흐름표</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>재고자산</t>
+          <t>법인세의 납부</t>
         </is>
       </c>
       <c r="C53" s="7" t="n">
-        <v>9319917000000</v>
+        <v>1170910000000</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>10396303000000</v>
+        <v>281339000000</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>1076386000000</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>5628008000000</v>
+      </c>
+      <c r="F53" s="7" t="n">
+        <v>5346669000000</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>1900.44</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>-75.97</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>재무상태표</t>
+          <t>현금흐름표</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>미지급금</t>
+          <t>재무활동 현금흐름</t>
         </is>
       </c>
       <c r="C54" s="7" t="n">
-        <v>5280304000000</v>
+        <v>6927433000000</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>6298382000000</v>
+        <v>-6874365000000</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>1018078000000</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>19.28</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>-2072321000000</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>4802044000000</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>재무상태표</t>
+          <t>현금흐름표</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>기타자본</t>
+          <t>단기금융상품의 감소</t>
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>-2191549000000</v>
+        <v>0</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>-1348598000000</v>
+        <v>272500000000</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>842951000000</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>3662500000000</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>3390000000000</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>1244.04</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>재무상태표</t>
+          <t>현금흐름표</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>이연법인세자산</t>
+          <t>배당금의 수취</t>
         </is>
       </c>
       <c r="C56" s="7" t="n">
-        <v>2016438000000</v>
+        <v>120008000000</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>2789409000000</v>
+        <v>189614000000</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>772971000000</v>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>38.33</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>2881608000000</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>2691994000000</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>1419.72</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>재무상태표</t>
+          <t>현금흐름표</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>현금및현금성자산</t>
+          <t>차입금의 차입</t>
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>2992694000000</v>
+        <v>17063997000000</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>2403922000000</v>
+        <v>6239628000000</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>-588772000000</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>-19.67</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>4296456000000</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>-1943172000000</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>-31.14</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>-63.43</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -4516,71 +4855,80 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>기말 현금및현금성자산</t>
+          <t>기타수취채권의 감소</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
-        <v>2992694000000</v>
+        <v>164928000000</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>2403922000000</v>
+        <v>2218030000000</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>-588772000000</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>-19.67</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>3620494000000</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>1402464000000</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>63.23</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>1244.85</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>재무상태표</t>
+          <t>현금흐름표</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>매입채무</t>
+          <t>기말 현금및현금성자산</t>
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>2824366000000</v>
+        <v>2898074000000</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>3317619000000</v>
+        <v>2992694000000</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>493253000000</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>17.46</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>2403922000000</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>-588772000000</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>-19.67</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F13:F59">
-    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="1">
+  <conditionalFormatting sqref="G13:G59">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>30.0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
       <formula>-30.0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="between" dxfId="0">
-      <formula>10.0</formula>
-      <formula>30.0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="between" dxfId="0">
-      <formula>-30.0</formula>
-      <formula>-10.0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4593,13 +4941,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E173"/>
+  <dimension ref="A1:E306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="125" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -4617,15 +4965,13 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>✓ 전체 158건 모두 일치 (검증 통과)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
+          <t>✓ 전체 291건 모두 일치 (검증 통과)</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -5080,19 +5426,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 부채및자본총계 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 부채및자본총계 (전전기)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>112412580000000</v>
+        <v>92949387000000</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>112412580000000</v>
+        <v>92949387000000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -5103,19 +5449,19 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 부채및자본총계 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 부채및자본총계 (전기)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>168903929000000</v>
+        <v>112412580000000</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>168903929000000</v>
+        <v>112412580000000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -5126,19 +5472,19 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 부채및자본총계</t>
+          <t>[스크리닝-원본금액] 재무상태표 부채및자본총계 (당기)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>50.25</v>
+        <v>168903929000000</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>50.25</v>
+        <v>168903929000000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -5149,19 +5495,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 자산총계 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 부채및자본총계</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>112412580000000</v>
+        <v>50.25</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>112412580000000</v>
+        <v>50.25</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -5172,19 +5518,19 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 자산총계 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 부채및자본총계</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>168903929000000</v>
+        <v>20.94</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>168903929000000</v>
+        <v>20.94</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -5195,19 +5541,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 자산총계</t>
+          <t>[스크리닝-추세이탈] 재무상태표 부채및자본총계</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>50.25</v>
+        <v>0</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>50.25</v>
+        <v>0</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -5218,19 +5564,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 자본총계 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 자산총계 (전전기)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>71227087000000</v>
+        <v>92949387000000</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>71227087000000</v>
+        <v>92949387000000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -5241,19 +5587,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 자본총계 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 자산총계 (전기)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>117318562000000</v>
+        <v>112412580000000</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>117318562000000</v>
+        <v>112412580000000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -5264,19 +5610,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 자본총계</t>
+          <t>[스크리닝-원본금액] 재무상태표 자산총계 (당기)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>64.70999999999999</v>
+        <v>168903929000000</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>64.70999999999999</v>
+        <v>168903929000000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -5287,19 +5633,19 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 이익잉여금 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 자산총계</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>65288998000000</v>
+        <v>50.25</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>65288998000000</v>
+        <v>50.25</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -5310,19 +5656,19 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 이익잉여금 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 자산총계</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>106222565000000</v>
+        <v>20.94</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>106222565000000</v>
+        <v>20.94</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -5333,19 +5679,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 이익잉여금</t>
+          <t>[스크리닝-추세이탈] 재무상태표 자산총계</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>62.7</v>
+        <v>0</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>62.7</v>
+        <v>0</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -5356,19 +5702,19 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 비유동자산 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 자본총계 (전전기)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>85202229000000</v>
+        <v>54518322000000</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>85202229000000</v>
+        <v>54518322000000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -5379,19 +5725,19 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 비유동자산 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 자본총계 (전기)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>122606991000000</v>
+        <v>71227087000000</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>122606991000000</v>
+        <v>71227087000000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -5402,19 +5748,19 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 비유동자산</t>
+          <t>[스크리닝-원본금액] 재무상태표 자본총계 (당기)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>43.9</v>
+        <v>117318562000000</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>43.9</v>
+        <v>117318562000000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -5425,19 +5771,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 매출액 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 자본총계</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>55736287000000</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>55736287000000</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -5448,19 +5794,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 매출액 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 자본총계</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>86852117000000</v>
+        <v>30.65</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>86852117000000</v>
+        <v>30.65</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -5471,19 +5817,19 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 포괄손익계산서 매출액</t>
+          <t>[스크리닝-추세이탈] 재무상태표 자본총계</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>55.83</v>
+        <v>0</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>55.83</v>
+        <v>0</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -5494,19 +5840,19 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 투자활동 현금흐름 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 이익잉여금 (전전기)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>-17268506000000</v>
+        <v>48734611000000</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>-17268506000000</v>
+        <v>48734611000000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -5517,19 +5863,19 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 투자활동 현금흐름 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 이익잉여금 (전기)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
-        <v>-46588841000000</v>
+        <v>65288998000000</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>-46588841000000</v>
+        <v>65288998000000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -5540,19 +5886,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 투자활동 현금흐름</t>
+          <t>[스크리닝-원본금액] 재무상태표 이익잉여금 (당기)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>-169.79</v>
+        <v>106222565000000</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>-169.79</v>
+        <v>106222565000000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -5563,19 +5909,19 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 법인세비용차감전순이익(손실) (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 이익잉여금</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>21271179000000</v>
+        <v>62.7</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>21271179000000</v>
+        <v>62.7</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -5586,19 +5932,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 법인세비용차감전순이익(손실) (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 이익잉여금</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>50058458000000</v>
+        <v>33.97</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>50058458000000</v>
+        <v>33.97</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -5609,19 +5955,19 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 포괄손익계산서 법인세비용차감전순이익(손실)</t>
+          <t>[스크리닝-추세이탈] 재무상태표 이익잉여금</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C54" s="5" t="n">
-        <v>135.33</v>
+        <v>0</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>135.33</v>
+        <v>0</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -5632,19 +5978,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 영업으로부터 창출된 현금흐름 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 비유동자산 (전전기)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>24479468000000</v>
+        <v>75198085000000</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>24479468000000</v>
+        <v>75198085000000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -5655,19 +6001,19 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 영업으로부터 창출된 현금흐름 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 비유동자산 (전기)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C56" s="5" t="n">
-        <v>51068852000000</v>
+        <v>85202229000000</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>51068852000000</v>
+        <v>85202229000000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -5678,19 +6024,19 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 영업으로부터 창출된 현금흐름</t>
+          <t>[스크리닝-원본금액] 재무상태표 비유동자산 (당기)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>108.62</v>
+        <v>122606991000000</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>108.62</v>
+        <v>122606991000000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -5701,19 +6047,19 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 총포괄이익(손실) (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 비유동자산</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>17381347000000</v>
+        <v>43.9</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>17381347000000</v>
+        <v>43.9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -5724,19 +6070,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 총포괄이익(손실) (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 비유동자산</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>42616584000000</v>
+        <v>13.3</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>42616584000000</v>
+        <v>13.3</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -5747,19 +6093,19 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 포괄손익계산서 총포괄이익(손실)</t>
+          <t>[스크리닝-추세이탈] 재무상태표 비유동자산</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
-        <v>145.19</v>
+        <v>0</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>145.19</v>
+        <v>0</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -5770,19 +6116,19 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 매출총이익(손실) (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 유동자산 (전전기)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>27580112000000</v>
+        <v>17751302000000</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>27580112000000</v>
+        <v>17751302000000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -5793,19 +6139,19 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 매출총이익(손실) (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 유동자산 (전기)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
-        <v>52760910000000</v>
+        <v>27210351000000</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>52760910000000</v>
+        <v>27210351000000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -5816,19 +6162,19 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 포괄손익계산서 매출총이익(손실)</t>
+          <t>[스크리닝-원본금액] 재무상태표 유동자산 (당기)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>91.3</v>
+        <v>46296938000000</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>91.3</v>
+        <v>46296938000000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -5839,19 +6185,19 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 당기순이익(손실) (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 유동자산</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>17640396000000</v>
+        <v>70.14</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>17640396000000</v>
+        <v>70.14</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -5862,19 +6208,19 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 당기순이익(손실) (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 유동자산</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>42688817000000</v>
+        <v>53.29</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>42688817000000</v>
+        <v>53.29</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -5885,19 +6231,19 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 포괄손익계산서 당기순이익(손실)</t>
+          <t>[스크리닝-추세이탈] 재무상태표 유동자산</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
-        <v>141.99</v>
+        <v>0</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>141.99</v>
+        <v>0</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -5908,19 +6254,19 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 영업활동 현금흐름 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 유형자산 (전전기)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>24197084000000</v>
+        <v>38974277000000</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>24197084000000</v>
+        <v>38974277000000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -5931,19 +6277,19 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 영업활동 현금흐름 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 유형자산 (전기)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C68" s="5" t="n">
-        <v>48093510000000</v>
+        <v>48316766000000</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>48093510000000</v>
+        <v>48316766000000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -5954,19 +6300,19 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 영업활동 현금흐름</t>
+          <t>[스크리닝-원본금액] 재무상태표 유형자산 (당기)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>98.76000000000001</v>
+        <v>67394741000000</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>98.76000000000001</v>
+        <v>67394741000000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -5977,19 +6323,19 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 영업이익(손실) (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 유형자산</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
-        <v>21331452000000</v>
+        <v>39.49</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>21331452000000</v>
+        <v>39.49</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -6000,19 +6346,19 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 영업이익(손실) (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 유형자산</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>44007409000000</v>
+        <v>23.97</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>44007409000000</v>
+        <v>23.97</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -6023,19 +6369,19 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 포괄손익계산서 영업이익(손실)</t>
+          <t>[스크리닝-추세이탈] 재무상태표 유형자산</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
-        <v>106.3</v>
+        <v>0</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>106.3</v>
+        <v>0</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -6046,19 +6392,19 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 유동자산 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 유동부채 (전전기)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>27210351000000</v>
+        <v>16197793000000</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>27210351000000</v>
+        <v>16197793000000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -6069,19 +6415,19 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 유동자산 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 유동부채 (전기)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C74" s="5" t="n">
-        <v>46296938000000</v>
+        <v>21577947000000</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>46296938000000</v>
+        <v>21577947000000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -6092,19 +6438,19 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 유동자산</t>
+          <t>[스크리닝-원본금액] 재무상태표 유동부채 (당기)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>70.14</v>
+        <v>34536586000000</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>70.14</v>
+        <v>34536586000000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -6115,19 +6461,19 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 유형자산 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 유동부채</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
-        <v>48316766000000</v>
+        <v>60.06</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>48316766000000</v>
+        <v>60.06</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -6138,19 +6484,19 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 유형자산 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 유동부채</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>67394741000000</v>
+        <v>33.22</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>67394741000000</v>
+        <v>33.22</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -6161,19 +6507,19 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 유형자산</t>
+          <t>[스크리닝-추세이탈] 재무상태표 유동부채</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C78" s="5" t="n">
-        <v>39.49</v>
+        <v>0</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>39.49</v>
+        <v>0</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -6184,19 +6530,19 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 단기금융상품의 증가 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 단기금융상품 (전전기)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>1902500000000</v>
+        <v>272500000000</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>1902500000000</v>
+        <v>272500000000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -6207,19 +6553,19 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 단기금융상품의 증가 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 단기금융상품 (전기)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C80" s="5" t="n">
-        <v>15832500000000</v>
+        <v>1902500000000</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>15832500000000</v>
+        <v>1902500000000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -6230,19 +6576,19 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 단기금융상품의 증가</t>
+          <t>[스크리닝-원본금액] 재무상태표 단기금융상품 (당기)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>732.1900000000001</v>
+        <v>14072500000000</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>732.1900000000001</v>
+        <v>14072500000000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -6253,19 +6599,19 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 금융수익 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 단기금융상품</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
-        <v>4848298000000</v>
+        <v>639.6799999999999</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>4848298000000</v>
+        <v>639.6799999999999</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -6276,19 +6622,19 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 금융수익 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 단기금융상품</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>17971786000000</v>
+        <v>598.17</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>17971786000000</v>
+        <v>598.17</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -6299,19 +6645,19 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 포괄손익계산서 금융수익</t>
+          <t>[스크리닝-추세이탈] 재무상태표 단기금융상품</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
-        <v>270.68</v>
+        <v>1</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>270.68</v>
+        <v>1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -6322,19 +6668,19 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 유동부채 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 장기투자자산 (전전기)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>21577947000000</v>
+        <v>3765853000000</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>21577947000000</v>
+        <v>3765853000000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -6345,19 +6691,19 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 유동부채 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 장기투자자산 (전기)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C86" s="5" t="n">
-        <v>34536586000000</v>
+        <v>3644169000000</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>34536586000000</v>
+        <v>3644169000000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -6368,19 +6714,19 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 유동부채</t>
+          <t>[스크리닝-원본금액] 재무상태표 장기투자자산 (당기)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>60.06</v>
+        <v>14285809000000</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>60.06</v>
+        <v>14285809000000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -6391,19 +6737,19 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 단기금융상품 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 장기투자자산</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C88" s="5" t="n">
-        <v>1902500000000</v>
+        <v>292.02</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>1902500000000</v>
+        <v>292.02</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -6414,19 +6760,19 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 단기금융상품 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 장기투자자산</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>14072500000000</v>
+        <v>-3.23</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>14072500000000</v>
+        <v>-3.23</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -6437,19 +6783,19 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 단기금융상품</t>
+          <t>[스크리닝-추세이탈] 재무상태표 장기투자자산</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C90" s="5" t="n">
-        <v>639.6799999999999</v>
+        <v>1</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>639.6799999999999</v>
+        <v>1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -6460,19 +6806,19 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 유형자산의 취득 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 부채총계 (전전기)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>15140313000000</v>
+        <v>38431065000000</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>15140313000000</v>
+        <v>38431065000000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -6483,19 +6829,19 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 유형자산의 취득 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 부채총계 (전기)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C92" s="5" t="n">
-        <v>26085216000000</v>
+        <v>41185493000000</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>26085216000000</v>
+        <v>41185493000000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -6506,19 +6852,19 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 유형자산의 취득</t>
+          <t>[스크리닝-원본금액] 재무상태표 부채총계 (당기)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>72.29000000000001</v>
+        <v>51585367000000</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>72.29000000000001</v>
+        <v>51585367000000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -6529,19 +6875,19 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 장기투자자산 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 부채총계</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C94" s="5" t="n">
-        <v>3644169000000</v>
+        <v>25.25</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>3644169000000</v>
+        <v>25.25</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -6552,19 +6898,19 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 장기투자자산 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 부채총계</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>14285809000000</v>
+        <v>7.17</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>14285809000000</v>
+        <v>7.17</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -6575,19 +6921,19 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 장기투자자산</t>
+          <t>[스크리닝-추세이탈] 재무상태표 부채총계</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C96" s="5" t="n">
-        <v>292.02</v>
+        <v>0</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>292.02</v>
+        <v>0</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -6598,19 +6944,19 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 부채총계 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 종속기업, 관계기업 및 공동기업투자 (전전기)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>41185493000000</v>
+        <v>12694398000000</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>41185493000000</v>
+        <v>12694398000000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -6621,19 +6967,19 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 부채총계 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 종속기업, 관계기업 및 공동기업투자 (전기)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C98" s="5" t="n">
-        <v>51585367000000</v>
+        <v>15112071000000</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>51585367000000</v>
+        <v>15112071000000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -6644,19 +6990,19 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 부채총계</t>
+          <t>[스크리닝-원본금액] 재무상태표 종속기업, 관계기업 및 공동기업투자 (당기)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>25.25</v>
+        <v>23555649000000</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>25.25</v>
+        <v>23555649000000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -6667,19 +7013,19 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 종속기업, 관계기업 및 공동기업투자 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 종속기업, 관계기업 및 공동기업투자</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C100" s="5" t="n">
-        <v>15112071000000</v>
+        <v>55.87</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>15112071000000</v>
+        <v>55.87</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -6690,19 +7036,19 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 종속기업, 관계기업 및 공동기업투자 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 종속기업, 관계기업 및 공동기업투자</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>23555649000000</v>
+        <v>19.05</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>23555649000000</v>
+        <v>19.05</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -6713,19 +7059,19 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 종속기업, 관계기업 및 공동기업투자</t>
+          <t>[스크리닝-추세이탈] 재무상태표 종속기업, 관계기업 및 공동기업투자</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C102" s="5" t="n">
-        <v>55.87</v>
+        <v>0</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>55.87</v>
+        <v>0</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -6736,19 +7082,19 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 차입금의 상환 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 매출채권 (전전기)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>11877832000000</v>
+        <v>3899437000000</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>11877832000000</v>
+        <v>3899437000000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -6759,19 +7105,19 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 차입금의 상환 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 매출채권 (전기)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C104" s="5" t="n">
-        <v>4235652000000</v>
+        <v>10342858000000</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>4235652000000</v>
+        <v>10342858000000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -6782,19 +7128,19 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 차입금의 상환</t>
+          <t>[스크리닝-원본금액] 재무상태표 매출채권 (당기)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>-64.34</v>
+        <v>16354297000000</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>-64.34</v>
+        <v>16354297000000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -6805,19 +7151,19 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 금융비용 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 매출채권</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C106" s="5" t="n">
-        <v>5085118000000</v>
+        <v>58.12</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>5085118000000</v>
+        <v>58.12</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -6828,19 +7174,19 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 금융비용 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 매출채권</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>11984187000000</v>
+        <v>165.24</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>11984187000000</v>
+        <v>165.24</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -6851,19 +7197,19 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 포괄손익계산서 금융비용</t>
+          <t>[스크리닝-추세이탈] 재무상태표 매출채권</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C108" s="5" t="n">
-        <v>135.67</v>
+        <v>1</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>135.67</v>
+        <v>1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -6874,19 +7220,19 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 매출채권 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 자본잉여금 (전전기)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>10342858000000</v>
+        <v>4389563000000</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>10342858000000</v>
+        <v>4389563000000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -6897,19 +7243,19 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 매출채권 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 자본잉여금 (전기)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C110" s="5" t="n">
-        <v>16354297000000</v>
+        <v>4465558000000</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>16354297000000</v>
+        <v>4465558000000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -6920,19 +7266,19 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 매출채권</t>
+          <t>[스크리닝-원본금액] 재무상태표 자본잉여금 (당기)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>58.12</v>
+        <v>8778664000000</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>58.12</v>
+        <v>8778664000000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -6943,19 +7289,19 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 매출원가 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 자본잉여금</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C112" s="5" t="n">
-        <v>28156175000000</v>
+        <v>96.59</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>28156175000000</v>
+        <v>96.59</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -6966,19 +7312,19 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 매출원가 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 자본잉여금</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>34091207000000</v>
+        <v>1.73</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>34091207000000</v>
+        <v>1.73</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -6989,19 +7335,19 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 포괄손익계산서 매출원가</t>
+          <t>[스크리닝-추세이탈] 재무상태표 자본잉여금</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C114" s="5" t="n">
-        <v>21.08</v>
+        <v>1</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>21.08</v>
+        <v>1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -7012,19 +7358,19 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 종속기업투자(MMT)의 순증감 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 당기법인세부채 (전전기)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>-1728082000000</v>
+        <v>4484000000</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>-1728082000000</v>
+        <v>4484000000</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -7035,19 +7381,19 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 종속기업투자(MMT)의 순증감 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 당기법인세부채 (전기)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C116" s="5" t="n">
-        <v>-7354446000000</v>
+        <v>2966606000000</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>-7354446000000</v>
+        <v>2966606000000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -7058,19 +7404,19 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 종속기업투자(MMT)의 순증감</t>
+          <t>[스크리닝-원본금액] 재무상태표 당기법인세부채 (당기)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>-325.58</v>
+        <v>6890244000000</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>-325.58</v>
+        <v>6890244000000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -7081,19 +7427,19 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 법인세의 납부 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 당기법인세부채</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C118" s="5" t="n">
-        <v>281339000000</v>
+        <v>132.26</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>281339000000</v>
+        <v>132.26</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -7104,19 +7450,19 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 법인세의 납부 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 당기법인세부채</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>5628008000000</v>
+        <v>66059.81</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>5628008000000</v>
+        <v>66059.81</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -7127,19 +7473,19 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 법인세의 납부</t>
+          <t>[스크리닝-추세이탈] 재무상태표 당기법인세부채</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C120" s="5" t="n">
-        <v>1900.44</v>
+        <v>1</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>1900.44</v>
+        <v>1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -7150,19 +7496,19 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 재무활동 현금흐름 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 비유동부채 (전전기)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>-6874365000000</v>
+        <v>22233272000000</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>-6874365000000</v>
+        <v>22233272000000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -7173,19 +7519,19 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 재무활동 현금흐름 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 비유동부채 (전기)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C122" s="5" t="n">
-        <v>-2072321000000</v>
+        <v>19607546000000</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>-2072321000000</v>
+        <v>19607546000000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -7196,19 +7542,19 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 재무활동 현금흐름</t>
+          <t>[스크리닝-원본금액] 재무상태표 비유동부채 (당기)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>69.84999999999999</v>
+        <v>17048781000000</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>69.84999999999999</v>
+        <v>17048781000000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -7219,19 +7565,19 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 자본잉여금 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 비유동부채</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C124" s="5" t="n">
-        <v>4465558000000</v>
+        <v>-13.05</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>4465558000000</v>
+        <v>-13.05</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -7242,19 +7588,19 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 자본잉여금 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 비유동부채</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>8778664000000</v>
+        <v>-11.81</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>8778664000000</v>
+        <v>-11.81</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -7265,19 +7611,19 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 자본잉여금</t>
+          <t>[스크리닝-추세이탈] 재무상태표 비유동부채</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C126" s="5" t="n">
-        <v>96.59</v>
+        <v>0</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>96.59</v>
+        <v>0</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -7288,19 +7634,19 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 당기법인세부채 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 재고자산 (전전기)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>2966606000000</v>
+        <v>8769507000000</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>2966606000000</v>
+        <v>8769507000000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -7311,19 +7657,19 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 당기법인세부채 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 재고자산 (전기)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C128" s="5" t="n">
-        <v>6890244000000</v>
+        <v>9319917000000</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>6890244000000</v>
+        <v>9319917000000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -7334,19 +7680,19 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 당기법인세부채</t>
+          <t>[스크리닝-원본금액] 재무상태표 재고자산 (당기)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>132.26</v>
+        <v>10396303000000</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>132.26</v>
+        <v>10396303000000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -7357,19 +7703,19 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 법인세비용(수익) (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 재고자산</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C130" s="5" t="n">
-        <v>3630783000000</v>
+        <v>11.55</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>3630783000000</v>
+        <v>11.55</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -7380,19 +7726,19 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 법인세비용(수익) (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 재고자산</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>7369641000000</v>
+        <v>6.28</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>7369641000000</v>
+        <v>6.28</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -7403,19 +7749,19 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 포괄손익계산서 법인세비용(수익)</t>
+          <t>[스크리닝-추세이탈] 재무상태표 재고자산</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C132" s="5" t="n">
-        <v>102.98</v>
+        <v>0</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>102.98</v>
+        <v>0</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -7426,19 +7772,19 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 단기금융상품의 감소 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 미지급금 (전전기)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>272500000000</v>
+        <v>3057580000000</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>272500000000</v>
+        <v>3057580000000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -7449,19 +7795,19 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 단기금융상품의 감소 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 미지급금 (전기)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C134" s="5" t="n">
-        <v>3662500000000</v>
+        <v>5280304000000</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>3662500000000</v>
+        <v>5280304000000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -7472,19 +7818,19 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 단기금융상품의 감소</t>
+          <t>[스크리닝-원본금액] 재무상태표 미지급금 (당기)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1244.04</v>
+        <v>6298382000000</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>1244.04</v>
+        <v>6298382000000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -7495,19 +7841,19 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 배당금의 수취 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 미지급금</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C136" s="5" t="n">
-        <v>189614000000</v>
+        <v>19.28</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>189614000000</v>
+        <v>19.28</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -7518,19 +7864,19 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 배당금의 수취 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 미지급금</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>2881608000000</v>
+        <v>72.7</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>2881608000000</v>
+        <v>72.7</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -7541,19 +7887,19 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 배당금의 수취</t>
+          <t>[스크리닝-추세이탈] 재무상태표 미지급금</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C138" s="5" t="n">
-        <v>1419.72</v>
+        <v>1</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>1419.72</v>
+        <v>1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -7564,19 +7910,19 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 비유동부채 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 기타자본 (전전기)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>19607546000000</v>
+        <v>-2269294000000</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>19607546000000</v>
+        <v>-2269294000000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -7587,19 +7933,19 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 비유동부채 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 기타자본 (전기)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C140" s="5" t="n">
-        <v>17048781000000</v>
+        <v>-2191549000000</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>17048781000000</v>
+        <v>-2191549000000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -7610,19 +7956,19 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 비유동부채</t>
+          <t>[스크리닝-원본금액] 재무상태표 기타자본 (당기)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>-13.05</v>
+        <v>-1348598000000</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>-13.05</v>
+        <v>-1348598000000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -7633,19 +7979,19 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 판매비와관리비 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 기타자본</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C142" s="5" t="n">
-        <v>6248660000000</v>
+        <v>38.46</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>6248660000000</v>
+        <v>38.46</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -7656,19 +8002,19 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 판매비와관리비 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 기타자본</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>8753501000000</v>
+        <v>3.43</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>8753501000000</v>
+        <v>3.43</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -7679,19 +8025,19 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 포괄손익계산서 판매비와관리비</t>
+          <t>[스크리닝-추세이탈] 재무상태표 기타자본</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C144" s="5" t="n">
-        <v>40.09</v>
+        <v>0</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>40.09</v>
+        <v>0</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -7702,19 +8048,19 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 차입금의 차입 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 이연법인세자산 (전전기)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>6239628000000</v>
+        <v>2318089000000</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>6239628000000</v>
+        <v>2318089000000</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -7725,19 +8071,19 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 차입금의 차입 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 이연법인세자산 (전기)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C146" s="5" t="n">
-        <v>4296456000000</v>
+        <v>2016438000000</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>4296456000000</v>
+        <v>2016438000000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -7748,19 +8094,19 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 차입금의 차입</t>
+          <t>[스크리닝-원본금액] 재무상태표 이연법인세자산 (당기)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>-31.14</v>
+        <v>2789409000000</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>-31.14</v>
+        <v>2789409000000</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -7771,19 +8117,19 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 기타수취채권의 감소 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 이연법인세자산</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C148" s="5" t="n">
-        <v>2218030000000</v>
+        <v>38.33</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>2218030000000</v>
+        <v>38.33</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -7794,19 +8140,19 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 기타수취채권의 감소 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 이연법인세자산</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>3620494000000</v>
+        <v>-13.01</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>3620494000000</v>
+        <v>-13.01</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -7817,19 +8163,19 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 기타수취채권의 감소</t>
+          <t>[스크리닝-추세이탈] 재무상태표 이연법인세자산</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C150" s="5" t="n">
-        <v>63.23</v>
+        <v>1</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>63.23</v>
+        <v>1</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -7840,19 +8186,19 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 재고자산 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 현금및현금성자산 (전전기)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>9319917000000</v>
+        <v>2898074000000</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>9319917000000</v>
+        <v>2898074000000</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -7863,19 +8209,19 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 재고자산 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 현금및현금성자산 (전기)</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C152" s="5" t="n">
-        <v>10396303000000</v>
+        <v>2992694000000</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>10396303000000</v>
+        <v>2992694000000</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -7886,19 +8232,19 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 재고자산</t>
+          <t>[스크리닝-원본금액] 재무상태표 현금및현금성자산 (당기)</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>11.55</v>
+        <v>2403922000000</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>11.55</v>
+        <v>2403922000000</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -7909,19 +8255,19 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 미지급금 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 현금및현금성자산</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C154" s="5" t="n">
-        <v>5280304000000</v>
+        <v>-19.67</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>5280304000000</v>
+        <v>-19.67</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -7932,19 +8278,19 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 미지급금 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 현금및현금성자산</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>6298382000000</v>
+        <v>3.26</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>6298382000000</v>
+        <v>3.26</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -7955,19 +8301,19 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 미지급금</t>
+          <t>[스크리닝-추세이탈] 재무상태표 현금및현금성자산</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C156" s="5" t="n">
-        <v>19.28</v>
+        <v>0</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>19.28</v>
+        <v>0</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -7978,19 +8324,19 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 기타자본 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 매입채무 (전전기)</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>-2191549000000</v>
+        <v>2410182000000</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>-2191549000000</v>
+        <v>2410182000000</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -8001,19 +8347,19 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 기타자본 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 매입채무 (전기)</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C158" s="5" t="n">
-        <v>-1348598000000</v>
+        <v>2824366000000</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>-1348598000000</v>
+        <v>2824366000000</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -8024,19 +8370,19 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 기타자본</t>
+          <t>[스크리닝-원본금액] 재무상태표 매입채무 (당기)</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>38.46</v>
+        <v>3317619000000</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>38.46</v>
+        <v>3317619000000</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -8047,19 +8393,19 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 이연법인세자산 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 매입채무</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C160" s="5" t="n">
-        <v>2016438000000</v>
+        <v>17.46</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>2016438000000</v>
+        <v>17.46</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -8070,19 +8416,19 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 이연법인세자산 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 매입채무</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>2789409000000</v>
+        <v>17.18</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>2789409000000</v>
+        <v>17.18</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -8093,19 +8439,19 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 이연법인세자산</t>
+          <t>[스크리닝-추세이탈] 재무상태표 매입채무</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C162" s="5" t="n">
-        <v>38.33</v>
+        <v>0</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>38.33</v>
+        <v>0</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -8116,19 +8462,19 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 현금및현금성자산 (전기)</t>
+          <t>[스크리닝-원본금액] 포괄손익계산서 매출액 (전전기)</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C163" s="5" t="n">
-        <v>2992694000000</v>
+        <v>27639997000000</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>2992694000000</v>
+        <v>27639997000000</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -8139,19 +8485,19 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 현금및현금성자산 (당기)</t>
+          <t>[스크리닝-원본금액] 포괄손익계산서 매출액 (전기)</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C164" s="5" t="n">
-        <v>2403922000000</v>
+        <v>55736287000000</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>2403922000000</v>
+        <v>55736287000000</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -8162,19 +8508,19 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 현금및현금성자산</t>
+          <t>[스크리닝-원본금액] 포괄손익계산서 매출액 (당기)</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C165" s="5" t="n">
-        <v>-19.67</v>
+        <v>86852117000000</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>-19.67</v>
+        <v>86852117000000</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -8185,19 +8531,19 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 기말 현금및현금성자산 (전기)</t>
+          <t>[스크리닝-증감률] 포괄손익계산서 매출액</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C166" s="5" t="n">
-        <v>2992694000000</v>
+        <v>55.83</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>2992694000000</v>
+        <v>55.83</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -8208,19 +8554,19 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 기말 현금및현금성자산 (당기)</t>
+          <t>[스크리닝-전전기증감률] 포괄손익계산서 매출액</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C167" s="5" t="n">
-        <v>2403922000000</v>
+        <v>101.65</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>2403922000000</v>
+        <v>101.65</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -8231,19 +8577,19 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 기말 현금및현금성자산</t>
+          <t>[스크리닝-추세이탈] 포괄손익계산서 매출액</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C168" s="5" t="n">
-        <v>-19.67</v>
+        <v>1</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>-19.67</v>
+        <v>1</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -8254,19 +8600,19 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 매입채무 (전기)</t>
+          <t>[스크리닝-원본금액] 포괄손익계산서 법인세비용차감전순이익(손실) (전전기)</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C169" s="5" t="n">
-        <v>2824366000000</v>
+        <v>-7578702000000</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>2824366000000</v>
+        <v>-7578702000000</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -8277,19 +8623,19 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 매입채무 (당기)</t>
+          <t>[스크리닝-원본금액] 포괄손익계산서 법인세비용차감전순이익(손실) (전기)</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C170" s="5" t="n">
-        <v>3317619000000</v>
+        <v>21271179000000</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>3317619000000</v>
+        <v>21271179000000</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -8300,19 +8646,19 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 매입채무</t>
+          <t>[스크리닝-원본금액] 포괄손익계산서 법인세비용차감전순이익(손실) (당기)</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C171" s="5" t="n">
-        <v>17.46</v>
+        <v>50058458000000</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>17.46</v>
+        <v>50058458000000</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -8323,7 +8669,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>스크리닝 완전성(포함됐어야 할 계정 누락 없음)</t>
+          <t>[스크리닝-증감률] 포괄손익계산서 법인세비용차감전순이익(손실)</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -8332,10 +8678,10 @@
         </is>
       </c>
       <c r="C172" s="5" t="n">
-        <v>0</v>
+        <v>135.33</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>0</v>
+        <v>135.33</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -8346,12 +8692,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>스크리닝 정확성(기준 미달 오탐 없음)</t>
+          <t>[스크리닝-추세이탈] 포괄손익계산서 법인세비용차감전순이익(손실)</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C173" s="5" t="n">
@@ -8361,6 +8707,3065 @@
         <v>0</v>
       </c>
       <c r="E173" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 총포괄이익(손실) (전전기)</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="n">
+        <v>-4874603000000</v>
+      </c>
+      <c r="D174" s="5" t="n">
+        <v>-4874603000000</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 총포괄이익(손실) (전기)</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="n">
+        <v>17381347000000</v>
+      </c>
+      <c r="D175" s="5" t="n">
+        <v>17381347000000</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 총포괄이익(손실) (당기)</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="n">
+        <v>42616584000000</v>
+      </c>
+      <c r="D176" s="5" t="n">
+        <v>42616584000000</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 총포괄이익(손실)</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="n">
+        <v>145.19</v>
+      </c>
+      <c r="D177" s="5" t="n">
+        <v>145.19</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 포괄손익계산서 총포괄이익(손실)</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 매출총이익(손실) (전전기)</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="n">
+        <v>447119000000</v>
+      </c>
+      <c r="D179" s="5" t="n">
+        <v>447119000000</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 매출총이익(손실) (전기)</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="n">
+        <v>27580112000000</v>
+      </c>
+      <c r="D180" s="5" t="n">
+        <v>27580112000000</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 매출총이익(손실) (당기)</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="n">
+        <v>52760910000000</v>
+      </c>
+      <c r="D181" s="5" t="n">
+        <v>52760910000000</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 매출총이익(손실)</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="D182" s="5" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 포괄손익계산서 매출총이익(손실)</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="n">
+        <v>6068.41</v>
+      </c>
+      <c r="D183" s="5" t="n">
+        <v>6068.41</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 포괄손익계산서 매출총이익(손실)</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D184" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 당기순이익(손실) (전전기)</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="n">
+        <v>-4836170000000</v>
+      </c>
+      <c r="D185" s="5" t="n">
+        <v>-4836170000000</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 당기순이익(손실) (전기)</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="n">
+        <v>17640396000000</v>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>17640396000000</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 당기순이익(손실) (당기)</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>42688817000000</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>42688817000000</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 당기순이익(손실)</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="n">
+        <v>141.99</v>
+      </c>
+      <c r="D188" s="5" t="n">
+        <v>141.99</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 포괄손익계산서 당기순이익(손실)</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 영업이익(손실) (전전기)</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>-4672124000000</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>-4672124000000</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 영업이익(손실) (전기)</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="n">
+        <v>21331452000000</v>
+      </c>
+      <c r="D191" s="5" t="n">
+        <v>21331452000000</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 영업이익(손실) (당기)</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="n">
+        <v>44007409000000</v>
+      </c>
+      <c r="D192" s="5" t="n">
+        <v>44007409000000</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 영업이익(손실)</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="D193" s="5" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 포괄손익계산서 영업이익(손실)</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 금융수익 (전전기)</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="n">
+        <v>2189851000000</v>
+      </c>
+      <c r="D195" s="5" t="n">
+        <v>2189851000000</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 금융수익 (전기)</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C196" s="5" t="n">
+        <v>4848298000000</v>
+      </c>
+      <c r="D196" s="5" t="n">
+        <v>4848298000000</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 금융수익 (당기)</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C197" s="5" t="n">
+        <v>17971786000000</v>
+      </c>
+      <c r="D197" s="5" t="n">
+        <v>17971786000000</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 금융수익</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="n">
+        <v>270.68</v>
+      </c>
+      <c r="D198" s="5" t="n">
+        <v>270.68</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 포괄손익계산서 금융수익</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C199" s="5" t="n">
+        <v>121.4</v>
+      </c>
+      <c r="D199" s="5" t="n">
+        <v>121.4</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 포괄손익계산서 금융수익</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C200" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D200" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 금융비용 (전전기)</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="n">
+        <v>5133547000000</v>
+      </c>
+      <c r="D201" s="5" t="n">
+        <v>5133547000000</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 금융비용 (전기)</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="n">
+        <v>5085118000000</v>
+      </c>
+      <c r="D202" s="5" t="n">
+        <v>5085118000000</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 금융비용 (당기)</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="n">
+        <v>11984187000000</v>
+      </c>
+      <c r="D203" s="5" t="n">
+        <v>11984187000000</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 금융비용</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="n">
+        <v>135.67</v>
+      </c>
+      <c r="D204" s="5" t="n">
+        <v>135.67</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 포괄손익계산서 금융비용</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="D205" s="5" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 포괄손익계산서 금융비용</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D206" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 매출원가 (전전기)</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="n">
+        <v>27192878000000</v>
+      </c>
+      <c r="D207" s="5" t="n">
+        <v>27192878000000</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 매출원가 (전기)</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="n">
+        <v>28156175000000</v>
+      </c>
+      <c r="D208" s="5" t="n">
+        <v>28156175000000</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 매출원가 (당기)</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C209" s="5" t="n">
+        <v>34091207000000</v>
+      </c>
+      <c r="D209" s="5" t="n">
+        <v>34091207000000</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 매출원가</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="D210" s="5" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 포괄손익계산서 매출원가</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="D211" s="5" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 포괄손익계산서 매출원가</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 법인세비용(수익) (전전기)</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="n">
+        <v>-2742532000000</v>
+      </c>
+      <c r="D213" s="5" t="n">
+        <v>-2742532000000</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 법인세비용(수익) (전기)</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C214" s="5" t="n">
+        <v>3630783000000</v>
+      </c>
+      <c r="D214" s="5" t="n">
+        <v>3630783000000</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 법인세비용(수익) (당기)</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C215" s="5" t="n">
+        <v>7369641000000</v>
+      </c>
+      <c r="D215" s="5" t="n">
+        <v>7369641000000</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 법인세비용(수익)</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C216" s="5" t="n">
+        <v>102.98</v>
+      </c>
+      <c r="D216" s="5" t="n">
+        <v>102.98</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 포괄손익계산서 법인세비용(수익)</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C217" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D217" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 판매비와관리비 (전전기)</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="n">
+        <v>5119243000000</v>
+      </c>
+      <c r="D218" s="5" t="n">
+        <v>5119243000000</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 판매비와관리비 (전기)</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C219" s="5" t="n">
+        <v>6248660000000</v>
+      </c>
+      <c r="D219" s="5" t="n">
+        <v>6248660000000</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 판매비와관리비 (당기)</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C220" s="5" t="n">
+        <v>8753501000000</v>
+      </c>
+      <c r="D220" s="5" t="n">
+        <v>8753501000000</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 판매비와관리비</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C221" s="5" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="D221" s="5" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 포괄손익계산서 판매비와관리비</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C222" s="5" t="n">
+        <v>22.06</v>
+      </c>
+      <c r="D222" s="5" t="n">
+        <v>22.06</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 포괄손익계산서 판매비와관리비</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D223" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 투자활동 현금흐름 (전전기)</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C224" s="5" t="n">
+        <v>-9232773000000</v>
+      </c>
+      <c r="D224" s="5" t="n">
+        <v>-9232773000000</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 투자활동 현금흐름 (전기)</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C225" s="5" t="n">
+        <v>-17268506000000</v>
+      </c>
+      <c r="D225" s="5" t="n">
+        <v>-17268506000000</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 투자활동 현금흐름 (당기)</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C226" s="5" t="n">
+        <v>-46588841000000</v>
+      </c>
+      <c r="D226" s="5" t="n">
+        <v>-46588841000000</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C227" s="5" t="n">
+        <v>-169.79</v>
+      </c>
+      <c r="D227" s="5" t="n">
+        <v>-169.79</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C228" s="5" t="n">
+        <v>-87.03</v>
+      </c>
+      <c r="D228" s="5" t="n">
+        <v>-87.03</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C229" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D229" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 영업으로부터 창출된 현금흐름 (전전기)</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C230" s="5" t="n">
+        <v>4888159000000</v>
+      </c>
+      <c r="D230" s="5" t="n">
+        <v>4888159000000</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 영업으로부터 창출된 현금흐름 (전기)</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C231" s="5" t="n">
+        <v>24479468000000</v>
+      </c>
+      <c r="D231" s="5" t="n">
+        <v>24479468000000</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 영업으로부터 창출된 현금흐름 (당기)</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C232" s="5" t="n">
+        <v>51068852000000</v>
+      </c>
+      <c r="D232" s="5" t="n">
+        <v>51068852000000</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 영업으로부터 창출된 현금흐름</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C233" s="5" t="n">
+        <v>108.62</v>
+      </c>
+      <c r="D233" s="5" t="n">
+        <v>108.62</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 영업으로부터 창출된 현금흐름</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C234" s="5" t="n">
+        <v>400.79</v>
+      </c>
+      <c r="D234" s="5" t="n">
+        <v>400.79</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 영업으로부터 창출된 현금흐름</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C235" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D235" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 영업활동 현금흐름 (전전기)</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C236" s="5" t="n">
+        <v>3591547000000</v>
+      </c>
+      <c r="D236" s="5" t="n">
+        <v>3591547000000</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 영업활동 현금흐름 (전기)</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C237" s="5" t="n">
+        <v>24197084000000</v>
+      </c>
+      <c r="D237" s="5" t="n">
+        <v>24197084000000</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 영업활동 현금흐름 (당기)</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C238" s="5" t="n">
+        <v>48093510000000</v>
+      </c>
+      <c r="D238" s="5" t="n">
+        <v>48093510000000</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C239" s="5" t="n">
+        <v>98.76000000000001</v>
+      </c>
+      <c r="D239" s="5" t="n">
+        <v>98.76000000000001</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C240" s="5" t="n">
+        <v>573.72</v>
+      </c>
+      <c r="D240" s="5" t="n">
+        <v>573.72</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C241" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D241" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 단기금융상품의 증가 (전전기)</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C242" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D242" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 단기금융상품의 증가 (전기)</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C243" s="5" t="n">
+        <v>1902500000000</v>
+      </c>
+      <c r="D243" s="5" t="n">
+        <v>1902500000000</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 단기금융상품의 증가 (당기)</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C244" s="5" t="n">
+        <v>15832500000000</v>
+      </c>
+      <c r="D244" s="5" t="n">
+        <v>15832500000000</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 단기금융상품의 증가</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C245" s="5" t="n">
+        <v>732.1900000000001</v>
+      </c>
+      <c r="D245" s="5" t="n">
+        <v>732.1900000000001</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 단기금융상품의 증가</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C246" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D246" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 유형자산의 취득 (전전기)</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C247" s="5" t="n">
+        <v>6707400000000</v>
+      </c>
+      <c r="D247" s="5" t="n">
+        <v>6707400000000</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 유형자산의 취득 (전기)</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C248" s="5" t="n">
+        <v>15140313000000</v>
+      </c>
+      <c r="D248" s="5" t="n">
+        <v>15140313000000</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 유형자산의 취득 (당기)</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C249" s="5" t="n">
+        <v>26085216000000</v>
+      </c>
+      <c r="D249" s="5" t="n">
+        <v>26085216000000</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 유형자산의 취득</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C250" s="5" t="n">
+        <v>72.29000000000001</v>
+      </c>
+      <c r="D250" s="5" t="n">
+        <v>72.29000000000001</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 유형자산의 취득</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C251" s="5" t="n">
+        <v>125.73</v>
+      </c>
+      <c r="D251" s="5" t="n">
+        <v>125.73</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 유형자산의 취득</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C252" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D252" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 차입금의 상환 (전전기)</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C253" s="5" t="n">
+        <v>9015663000000</v>
+      </c>
+      <c r="D253" s="5" t="n">
+        <v>9015663000000</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 차입금의 상환 (전기)</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C254" s="5" t="n">
+        <v>11877832000000</v>
+      </c>
+      <c r="D254" s="5" t="n">
+        <v>11877832000000</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 차입금의 상환 (당기)</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C255" s="5" t="n">
+        <v>4235652000000</v>
+      </c>
+      <c r="D255" s="5" t="n">
+        <v>4235652000000</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 차입금의 상환</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C256" s="5" t="n">
+        <v>-64.34</v>
+      </c>
+      <c r="D256" s="5" t="n">
+        <v>-64.34</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 차입금의 상환</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C257" s="5" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="D257" s="5" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 차입금의 상환</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C258" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D258" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 종속기업투자(MMT)의 순증감 (전전기)</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C259" s="5" t="n">
+        <v>-755395000000</v>
+      </c>
+      <c r="D259" s="5" t="n">
+        <v>-755395000000</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 종속기업투자(MMT)의 순증감 (전기)</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C260" s="5" t="n">
+        <v>-1728082000000</v>
+      </c>
+      <c r="D260" s="5" t="n">
+        <v>-1728082000000</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 종속기업투자(MMT)의 순증감 (당기)</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C261" s="5" t="n">
+        <v>-7354446000000</v>
+      </c>
+      <c r="D261" s="5" t="n">
+        <v>-7354446000000</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 종속기업투자(MMT)의 순증감</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C262" s="5" t="n">
+        <v>-325.58</v>
+      </c>
+      <c r="D262" s="5" t="n">
+        <v>-325.58</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 종속기업투자(MMT)의 순증감</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C263" s="5" t="n">
+        <v>-128.77</v>
+      </c>
+      <c r="D263" s="5" t="n">
+        <v>-128.77</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 종속기업투자(MMT)의 순증감</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C264" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D264" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 법인세의 납부 (전전기)</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="n">
+        <v>1170910000000</v>
+      </c>
+      <c r="D265" s="5" t="n">
+        <v>1170910000000</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 법인세의 납부 (전기)</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C266" s="5" t="n">
+        <v>281339000000</v>
+      </c>
+      <c r="D266" s="5" t="n">
+        <v>281339000000</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 법인세의 납부 (당기)</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C267" s="5" t="n">
+        <v>5628008000000</v>
+      </c>
+      <c r="D267" s="5" t="n">
+        <v>5628008000000</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 법인세의 납부</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C268" s="5" t="n">
+        <v>1900.44</v>
+      </c>
+      <c r="D268" s="5" t="n">
+        <v>1900.44</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 법인세의 납부</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C269" s="5" t="n">
+        <v>-75.97</v>
+      </c>
+      <c r="D269" s="5" t="n">
+        <v>-75.97</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 법인세의 납부</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C270" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D270" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 재무활동 현금흐름 (전전기)</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C271" s="5" t="n">
+        <v>6927433000000</v>
+      </c>
+      <c r="D271" s="5" t="n">
+        <v>6927433000000</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 재무활동 현금흐름 (전기)</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C272" s="5" t="n">
+        <v>-6874365000000</v>
+      </c>
+      <c r="D272" s="5" t="n">
+        <v>-6874365000000</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 재무활동 현금흐름 (당기)</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C273" s="5" t="n">
+        <v>-2072321000000</v>
+      </c>
+      <c r="D273" s="5" t="n">
+        <v>-2072321000000</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C274" s="5" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="D274" s="5" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C275" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D275" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 단기금융상품의 감소 (전전기)</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C276" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D276" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 단기금융상품의 감소 (전기)</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C277" s="5" t="n">
+        <v>272500000000</v>
+      </c>
+      <c r="D277" s="5" t="n">
+        <v>272500000000</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 단기금융상품의 감소 (당기)</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C278" s="5" t="n">
+        <v>3662500000000</v>
+      </c>
+      <c r="D278" s="5" t="n">
+        <v>3662500000000</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 단기금융상품의 감소</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C279" s="5" t="n">
+        <v>1244.04</v>
+      </c>
+      <c r="D279" s="5" t="n">
+        <v>1244.04</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 단기금융상품의 감소</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C280" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D280" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 배당금의 수취 (전전기)</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C281" s="5" t="n">
+        <v>120008000000</v>
+      </c>
+      <c r="D281" s="5" t="n">
+        <v>120008000000</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 배당금의 수취 (전기)</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C282" s="5" t="n">
+        <v>189614000000</v>
+      </c>
+      <c r="D282" s="5" t="n">
+        <v>189614000000</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 배당금의 수취 (당기)</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C283" s="5" t="n">
+        <v>2881608000000</v>
+      </c>
+      <c r="D283" s="5" t="n">
+        <v>2881608000000</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 배당금의 수취</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C284" s="5" t="n">
+        <v>1419.72</v>
+      </c>
+      <c r="D284" s="5" t="n">
+        <v>1419.72</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 배당금의 수취</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C285" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="D285" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 배당금의 수취</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C286" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D286" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 차입금의 차입 (전전기)</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C287" s="5" t="n">
+        <v>17063997000000</v>
+      </c>
+      <c r="D287" s="5" t="n">
+        <v>17063997000000</v>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 차입금의 차입 (전기)</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C288" s="5" t="n">
+        <v>6239628000000</v>
+      </c>
+      <c r="D288" s="5" t="n">
+        <v>6239628000000</v>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 차입금의 차입 (당기)</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C289" s="5" t="n">
+        <v>4296456000000</v>
+      </c>
+      <c r="D289" s="5" t="n">
+        <v>4296456000000</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 차입금의 차입</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C290" s="5" t="n">
+        <v>-31.14</v>
+      </c>
+      <c r="D290" s="5" t="n">
+        <v>-31.14</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 차입금의 차입</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C291" s="5" t="n">
+        <v>-63.43</v>
+      </c>
+      <c r="D291" s="5" t="n">
+        <v>-63.43</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 차입금의 차입</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C292" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D292" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기타수취채권의 감소 (전전기)</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C293" s="5" t="n">
+        <v>164928000000</v>
+      </c>
+      <c r="D293" s="5" t="n">
+        <v>164928000000</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기타수취채권의 감소 (전기)</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C294" s="5" t="n">
+        <v>2218030000000</v>
+      </c>
+      <c r="D294" s="5" t="n">
+        <v>2218030000000</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기타수취채권의 감소 (당기)</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C295" s="5" t="n">
+        <v>3620494000000</v>
+      </c>
+      <c r="D295" s="5" t="n">
+        <v>3620494000000</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 기타수취채권의 감소</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C296" s="5" t="n">
+        <v>63.23</v>
+      </c>
+      <c r="D296" s="5" t="n">
+        <v>63.23</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 기타수취채권의 감소</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C297" s="5" t="n">
+        <v>1244.85</v>
+      </c>
+      <c r="D297" s="5" t="n">
+        <v>1244.85</v>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 기타수취채권의 감소</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C298" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D298" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기말 현금및현금성자산 (전전기)</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C299" s="5" t="n">
+        <v>2898074000000</v>
+      </c>
+      <c r="D299" s="5" t="n">
+        <v>2898074000000</v>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기말 현금및현금성자산 (전기)</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C300" s="5" t="n">
+        <v>2992694000000</v>
+      </c>
+      <c r="D300" s="5" t="n">
+        <v>2992694000000</v>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기말 현금및현금성자산 (당기)</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C301" s="5" t="n">
+        <v>2403922000000</v>
+      </c>
+      <c r="D301" s="5" t="n">
+        <v>2403922000000</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 기말 현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C302" s="5" t="n">
+        <v>-19.67</v>
+      </c>
+      <c r="D302" s="5" t="n">
+        <v>-19.67</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 기말 현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C303" s="5" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="D303" s="5" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 기말 현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C304" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D304" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>스크리닝 완전성(포함됐어야 할 계정 누락 없음)</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C305" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D305" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>스크리닝 정확성(기준 미달 오탐 없음)</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C306" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D306" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E306" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
